--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486677_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486677_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.564500000000001</v>
+        <v>8.731299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2706</v>
+        <v>6.636</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2939</v>
+        <v>2.0952</v>
       </c>
       <c r="G2" t="n">
         <v>7.4289</v>
@@ -610,13 +610,13 @@
         <v>2.51</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6287</v>
+        <v>-0.4619</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5245</v>
+        <v>-0.1591</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1042</v>
+        <v>-0.3028</v>
       </c>
       <c r="V2" t="n">
         <v>1.1851</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7159</v>
+        <v>3.1573</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5728</v>
+        <v>-0.883</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2887</v>
+        <v>4.0403</v>
       </c>
       <c r="G3" t="n">
         <v>2.5696</v>
@@ -688,13 +688,13 @@
         <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4136</v>
+        <v>-0.9722</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4142</v>
+        <v>-0.7244</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.2477</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3709</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8829</v>
+        <v>1.738</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7156</v>
+        <v>-0.6121</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5985</v>
+        <v>2.3502</v>
       </c>
       <c r="G4" t="n">
         <v>2.663</v>
@@ -766,13 +766,13 @@
         <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9651999999999999</v>
+        <v>-1.1101</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7453</v>
+        <v>-0.6418</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2199</v>
+        <v>-0.4682</v>
       </c>
       <c r="V4" t="n">
         <v>0.5712</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4641</v>
+        <v>1.0805</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.049</v>
+        <v>-1.5319</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5131</v>
+        <v>2.6124</v>
       </c>
       <c r="G5" t="n">
         <v>-0.1538</v>
@@ -844,13 +844,13 @@
         <v>2.3169</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.699</v>
+        <v>-1.0826</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3796</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3195</v>
+        <v>-0.2201</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4007</v>
+        <v>0.7869</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.827</v>
+        <v>-0.5649</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2276</v>
+        <v>1.3518</v>
       </c>
       <c r="G6" t="n">
         <v>1.7495</v>
@@ -922,13 +922,13 @@
         <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0206</v>
+        <v>-0.6344</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5245</v>
+        <v>-0.2625</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4961</v>
+        <v>-0.3719</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3282</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.335</v>
+        <v>0.6218</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.3785</v>
+        <v>-1.1165</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7135</v>
+        <v>1.7383</v>
       </c>
       <c r="G7" t="n">
         <v>-2.3105</v>
@@ -1000,13 +1000,13 @@
         <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9764</v>
+        <v>-0.6895</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8277</v>
+        <v>-0.5657</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1486</v>
+        <v>-0.1238</v>
       </c>
       <c r="V7" t="n">
         <v>1.8842</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. REYES ZUR</t>
+          <t>B. SOW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1089</v>
+        <v>0.0728</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2826</v>
+        <v>-0.1793</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3914</v>
+        <v>0.2522</v>
       </c>
       <c r="G8" t="n">
-        <v>0.462</v>
+        <v>0.1103</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0483</v>
+        <v>-0.1655</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4137</v>
+        <v>0.2758</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3244</v>
+        <v>0.0414</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3244</v>
+        <v>0.0414</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1376</v>
+        <v>0.0689</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2761</v>
+        <v>-0.2069</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4137</v>
+        <v>0.2758</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3862</v>
+        <v>0.3862</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S8" t="n">
-        <v>0.033</v>
+        <v>-0.138</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3584</v>
+        <v>-0.2207</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3254</v>
+        <v>0.0828</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. SOW</t>
+          <t>P. REYES ZUR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.032</v>
+        <v>0.0551</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2345</v>
+        <v>-0.386</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2025</v>
+        <v>0.4411</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1103</v>
+        <v>0.462</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1655</v>
+        <v>0.0483</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2758</v>
+        <v>0.4137</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0414</v>
+        <v>0.3244</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0414</v>
+        <v>0.3244</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0689</v>
+        <v>0.1376</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2069</v>
+        <v>-0.2761</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2758</v>
+        <v>0.4137</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3862</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2428</v>
+        <v>-0.0208</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2759</v>
+        <v>0.255</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0331</v>
+        <v>-0.2757</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3597</v>
+        <v>-0.9595</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1015</v>
+        <v>-0.6224</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4613</v>
+        <v>-0.3371</v>
       </c>
       <c r="G10" t="n">
         <v>0.6891</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6342</v>
+        <v>0.0344</v>
       </c>
       <c r="T10" t="n">
-        <v>1.103</v>
+        <v>0.3791</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4688</v>
+        <v>-0.3447</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4554</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1185</v>
+        <v>-1.2012</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2007</v>
+        <v>-0.4076</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9177</v>
+        <v>-0.7936</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8631</v>
@@ -1312,13 +1312,13 @@
         <v>0.7723</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0277</v>
+        <v>-0.1104</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3032</v>
+        <v>0.0964</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3309</v>
+        <v>-0.2068</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4803</v>
+        <v>-3.5038</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0344</v>
+        <v>-4.0826</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5541</v>
+        <v>0.5789</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3314</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.149</v>
+        <v>-0.1724</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1928</v>
+        <v>0.1446</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3418</v>
+        <v>-0.317</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1699</v>
+        <v>-3.9919</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3429</v>
+        <v>-3.2395</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.827</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>0.2963</v>
@@ -1468,13 +1468,13 @@
         <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0261</v>
+        <v>-0.8482</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7174</v>
+        <v>-0.6139</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3087</v>
+        <v>-0.2342</v>
       </c>
       <c r="V13" t="n">
         <v>-3.4401</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3116</v>
+        <v>6.587300000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.265899999999999</v>
+        <v>-6.989800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>13.5773</v>
+        <v>13.5772</v>
       </c>
       <c r="G14" t="n">
         <v>8.309900000000001</v>
@@ -1546,13 +1546,13 @@
         <v>17.377</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.4819</v>
+        <v>-6.206100000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.4517</v>
+        <v>-3.1754</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.0302</v>
+        <v>-3.0301</v>
       </c>
       <c r="V14" t="n">
         <v>-3.2397</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5664</v>
+        <v>3.1406</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4944</v>
+        <v>1.9536</v>
       </c>
       <c r="F15" t="n">
-        <v>1.072</v>
+        <v>1.187</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9904</v>
+        <v>2.6151</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3312</v>
+        <v>1.3583</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3216</v>
+        <v>1.2569</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7707</v>
+        <v>1.7057</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4279</v>
+        <v>1.0139</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3428</v>
+        <v>0.6918</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2197</v>
+        <v>0.9095</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7591</v>
+        <v>0.3443</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9788</v>
+        <v>0.5651</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3169</v>
+        <v>-0.1931</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4215</v>
+        <v>0.2621</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4267</v>
+        <v>0.441</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0052</v>
+        <v>-0.1789</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6991000000000001</v>
+        <v>-0.1228</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0852</v>
+        <v>-0.1228</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3851</v>
+        <v>2.8473</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7743</v>
+        <v>1.3607</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6108</v>
+        <v>1.4866</v>
       </c>
       <c r="G16" t="n">
         <v>1.1255</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1514</v>
+        <v>1.6136</v>
       </c>
       <c r="T16" t="n">
-        <v>1.075</v>
+        <v>0.6614</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0764</v>
+        <v>0.9522</v>
       </c>
       <c r="V16" t="n">
         <v>2.6182</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0825</v>
+        <v>2.6274</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3673</v>
+        <v>1.3567</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7151999999999999</v>
+        <v>1.2707</v>
       </c>
       <c r="G17" t="n">
-        <v>2.6151</v>
+        <v>1.9904</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3583</v>
+        <v>-0.3312</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2569</v>
+        <v>2.3216</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7057</v>
+        <v>1.7707</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0139</v>
+        <v>0.4279</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6918</v>
+        <v>1.3428</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9095</v>
+        <v>0.2197</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3443</v>
+        <v>-0.7591</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5651</v>
+        <v>0.9788</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1931</v>
+        <v>-2.3169</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2039</v>
+        <v>1.4825</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8547</v>
+        <v>1.2891</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6506999999999999</v>
+        <v>0.1934</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1228</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1228</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0074</v>
+        <v>-0.7869</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0833</v>
+        <v>-1.7039</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0908</v>
+        <v>0.9169</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6144</v>
@@ -1858,13 +1858,13 @@
         <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2357</v>
+        <v>0.4413</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0754</v>
+        <v>0.4549</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1603</v>
+        <v>-0.0136</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>L. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1638</v>
+        <v>-1.214</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.907</v>
+        <v>-0.862</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7432</v>
+        <v>-0.352</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6633</v>
+        <v>-0.6209</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9174</v>
+        <v>-0.214</v>
       </c>
       <c r="I19" t="n">
-        <v>-3.5807</v>
+        <v>-0.4069</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4408</v>
+        <v>0.0621</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8497</v>
+        <v>0.0621</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.2905</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2225</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9323</v>
+        <v>-0.2761</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7098</v>
+        <v>-0.4069</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5446</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0892</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8539</v>
+        <v>0.1793</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2764</v>
+        <v>0.0413</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1303</v>
+        <v>0.138</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1902</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8995</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2907</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. FLORES LUCAS</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.4705</v>
+        <v>-1.5696</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0689</v>
+        <v>-3.4933</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4017</v>
+        <v>1.9237</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6209</v>
+        <v>-2.6633</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.214</v>
+        <v>0.9174</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4069</v>
+        <v>-3.5807</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0621</v>
+        <v>-1.4408</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0621</v>
+        <v>2.8497</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-4.2905</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-1.2225</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2761</v>
+        <v>-1.9323</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4069</v>
+        <v>0.7098</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7723</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>-3.0892</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.07729999999999999</v>
+        <v>1.4482</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1655</v>
+        <v>0.1373</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0883</v>
+        <v>1.3109</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.1902</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8995</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.2907</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.905</v>
+        <v>-2.405</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4015</v>
+        <v>-4.8337</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4966</v>
+        <v>2.4287</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4817</v>
+        <v>-2.7442</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6761</v>
+        <v>-0.877</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1944</v>
+        <v>-1.8673</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.1837</v>
+        <v>-2.0735</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5372</v>
+        <v>0.6415</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6465</v>
+        <v>-2.7149</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.298</v>
+        <v>-0.6707</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.1389</v>
+        <v>-1.5184</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8409</v>
+        <v>0.8477</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.7377</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0892</v>
+        <v>-2.1239</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7006</v>
+        <v>0.8481</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.028</v>
+        <v>0.0201</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7286</v>
+        <v>0.828</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6138</v>
+        <v>-0.1228</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8995</v>
+        <v>-0.6565</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2856</v>
+        <v>0.5337</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2213</v>
+        <v>-2.5593</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4496</v>
+        <v>-2.0359</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.5234</v>
       </c>
       <c r="G22" t="n">
         <v>-3.0807</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0758</v>
+        <v>-0.4137</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4139</v>
+        <v>-0.0002</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6618000000000001</v>
+        <v>-0.4135</v>
       </c>
       <c r="V22" t="n">
         <v>0.1628</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3855</v>
+        <v>-2.723</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.7645</v>
+        <v>-3.1947</v>
       </c>
       <c r="F23" t="n">
-        <v>2.379</v>
+        <v>0.4717</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.7442</v>
+        <v>-2.4817</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.877</v>
+        <v>-2.6761</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8673</v>
+        <v>0.1944</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.0735</v>
+        <v>-1.1837</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6415</v>
+        <v>-0.5372</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.7149</v>
+        <v>-0.6465</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6707</v>
+        <v>-1.298</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.5184</v>
+        <v>-2.1389</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8477</v>
+        <v>0.8409</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3862</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1239</v>
+        <v>-3.0892</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1323</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9107</v>
+        <v>0.1788</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7784</v>
+        <v>0.7037</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1228</v>
+        <v>0.6138</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6565</v>
+        <v>0.8995</v>
       </c>
       <c r="X23" t="n">
-        <v>0.5337</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2068</v>
+        <v>-3.6689</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5384</v>
+        <v>-2.1247</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6684</v>
+        <v>-1.5442</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8357</v>
@@ -2326,13 +2326,13 @@
         <v>0.3862</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.2621</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.607</v>
+        <v>-0.1933</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1929</v>
+        <v>-0.0687</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7989</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.311500000000001</v>
+        <v>-6.311399999999999</v>
       </c>
       <c r="E25" t="n">
         <v>-13.5772</v>
       </c>
       <c r="F25" t="n">
-        <v>7.2658</v>
+        <v>7.265700000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-8.309900000000001</v>
@@ -2374,19 +2374,19 @@
         <v>-4.1392</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.1707</v>
+        <v>-4.170699999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.298999999999999</v>
+        <v>-4.299000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>5.523</v>
       </c>
       <c r="L25" t="n">
-        <v>-9.8218</v>
+        <v>-9.821799999999998</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.010800000000001</v>
+        <v>-4.0108</v>
       </c>
       <c r="N25" t="n">
         <v>-9.6622</v>
@@ -2404,19 +2404,19 @@
         <v>9.6538</v>
       </c>
       <c r="S25" t="n">
-        <v>6.481700000000002</v>
+        <v>6.4819</v>
       </c>
       <c r="T25" t="n">
-        <v>3.0303</v>
+        <v>3.0304</v>
       </c>
       <c r="U25" t="n">
-        <v>3.4517</v>
+        <v>3.4515</v>
       </c>
       <c r="V25" t="n">
         <v>3.2396</v>
       </c>
       <c r="W25" t="n">
-        <v>5.068499999999999</v>
+        <v>5.0685</v>
       </c>
       <c r="X25" t="n">
         <v>-1.8289</v>
